--- a/Data/EXCEL/Transfer/salemon/202206/6841-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6841-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B99B7B35-D670-45F2-B360-8B20C1857967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B253F0D-916B-4D07-9FA9-949D82004815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6841-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,19 +1218,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="13" width="11.5" customWidth="1"/>
-    <col min="14" max="14" width="10.125" customWidth="1"/>
-    <col min="15" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="12.625" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="13" width="13.25" customWidth="1"/>
+    <col min="14" max="14" width="11.5" customWidth="1"/>
+    <col min="15" max="16" width="13.25" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1383,537 +1383,537 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="C5" s="7">
-        <v>88.3</v>
+        <v>89</v>
       </c>
       <c r="D5" s="7">
-        <v>91.9</v>
+        <v>100.5</v>
       </c>
       <c r="E5" s="7">
-        <v>79.900000000000006</v>
+        <v>85.1</v>
       </c>
       <c r="F5" s="8">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="G5" s="8">
-        <v>3.88</v>
+        <v>0.79</v>
       </c>
       <c r="H5" s="9">
-        <v>3.5999999999999997E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="I5" s="8">
-        <v>59.3</v>
+        <v>140.19999999999999</v>
       </c>
       <c r="J5" s="8">
-        <v>269.10000000000002</v>
+        <v>2223.9</v>
       </c>
       <c r="K5" s="9">
-        <v>0.14699999999999999</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="L5" s="10">
-        <v>-48.8</v>
+        <v>-19.7</v>
       </c>
       <c r="M5" s="9">
-        <v>3.5999999999999997E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="N5" s="8">
-        <v>59.3</v>
+        <v>140.19999999999999</v>
       </c>
       <c r="O5" s="8">
-        <v>269.10000000000002</v>
+        <v>2223.9</v>
       </c>
       <c r="P5" s="9">
-        <v>0.14699999999999999</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="Q5" s="10">
-        <v>-48.8</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="C6" s="7">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="D6" s="7">
-        <v>112</v>
+        <v>91.9</v>
       </c>
       <c r="E6" s="7">
-        <v>84</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-29</v>
-      </c>
-      <c r="G6" s="10">
-        <v>-25.44</v>
+        <v>79.900000000000006</v>
+      </c>
+      <c r="F6" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G6" s="8">
+        <v>3.88</v>
       </c>
       <c r="H6" s="9">
-        <v>2.2599999999999999E-2</v>
-      </c>
-      <c r="I6" s="10">
-        <v>-49.8</v>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>59.3</v>
       </c>
       <c r="J6" s="8">
-        <v>564.4</v>
+        <v>269.10000000000002</v>
       </c>
       <c r="K6" s="9">
-        <v>0.111</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="L6" s="10">
-        <v>-60</v>
+        <v>-48.8</v>
       </c>
       <c r="M6" s="9">
-        <v>2.2599999999999999E-2</v>
-      </c>
-      <c r="N6" s="10">
-        <v>-49.8</v>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="N6" s="8">
+        <v>59.3</v>
       </c>
       <c r="O6" s="8">
-        <v>564.4</v>
+        <v>269.10000000000002</v>
       </c>
       <c r="P6" s="9">
-        <v>0.111</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="Q6" s="10">
-        <v>-60</v>
+        <v>-48.8</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C7" s="7">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="D7" s="7">
-        <v>130.5</v>
+        <v>112</v>
       </c>
       <c r="E7" s="7">
-        <v>89.7</v>
-      </c>
-      <c r="F7" s="8">
-        <v>5</v>
-      </c>
-      <c r="G7" s="8">
-        <v>4.59</v>
+        <v>84</v>
+      </c>
+      <c r="F7" s="10">
+        <v>-29</v>
+      </c>
+      <c r="G7" s="10">
+        <v>-25.44</v>
       </c>
       <c r="H7" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>43.6</v>
-      </c>
-      <c r="J7" s="10">
-        <v>-83.4</v>
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="I7" s="10">
+        <v>-49.8</v>
+      </c>
+      <c r="J7" s="8">
+        <v>564.4</v>
       </c>
       <c r="K7" s="9">
-        <v>8.8300000000000003E-2</v>
+        <v>0.111</v>
       </c>
       <c r="L7" s="10">
-        <v>-67.8</v>
+        <v>-60</v>
       </c>
       <c r="M7" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="N7" s="8">
-        <v>43.6</v>
-      </c>
-      <c r="O7" s="10">
-        <v>-83.4</v>
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="N7" s="10">
+        <v>-49.8</v>
+      </c>
+      <c r="O7" s="8">
+        <v>564.4</v>
       </c>
       <c r="P7" s="9">
-        <v>8.8300000000000003E-2</v>
+        <v>0.111</v>
       </c>
       <c r="Q7" s="10">
-        <v>-67.8</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>115.5</v>
+        <v>109</v>
       </c>
       <c r="C8" s="7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D8" s="7">
-        <v>121</v>
+        <v>130.5</v>
       </c>
       <c r="E8" s="7">
-        <v>108.5</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-6.5</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-5.63</v>
+        <v>89.7</v>
+      </c>
+      <c r="F8" s="8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>4.59</v>
       </c>
       <c r="H8" s="9">
-        <v>3.1300000000000001E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I8" s="8">
-        <v>160</v>
-      </c>
-      <c r="J8" s="8">
-        <v>3339.6</v>
+        <v>43.6</v>
+      </c>
+      <c r="J8" s="10">
+        <v>-83.4</v>
       </c>
       <c r="K8" s="9">
-        <v>4.3299999999999998E-2</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1579.8</v>
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="L8" s="10">
+        <v>-67.8</v>
       </c>
       <c r="M8" s="9">
-        <v>3.1300000000000001E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="N8" s="8">
-        <v>160</v>
-      </c>
-      <c r="O8" s="8">
-        <v>3339.6</v>
+        <v>43.6</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-83.4</v>
       </c>
       <c r="P8" s="9">
-        <v>4.3299999999999998E-2</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>1579.8</v>
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>-67.8</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>145</v>
+        <v>115.5</v>
       </c>
       <c r="C9" s="7">
-        <v>115.5</v>
+        <v>109</v>
       </c>
       <c r="D9" s="7">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="E9" s="7">
-        <v>115</v>
+        <v>108.5</v>
       </c>
       <c r="F9" s="10">
-        <v>-29.5</v>
+        <v>-6.5</v>
       </c>
       <c r="G9" s="10">
-        <v>-20.34</v>
+        <v>-5.63</v>
       </c>
       <c r="H9" s="9">
-        <v>1.2E-2</v>
-      </c>
-      <c r="I9" s="10">
-        <v>-34.5</v>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="I9" s="8">
+        <v>160</v>
       </c>
       <c r="J9" s="8">
-        <v>621</v>
+        <v>3339.6</v>
       </c>
       <c r="K9" s="9">
-        <v>1.2E-2</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="L9" s="8">
-        <v>621</v>
+        <v>1579.8</v>
       </c>
       <c r="M9" s="9">
-        <v>1.2E-2</v>
-      </c>
-      <c r="N9" s="10">
-        <v>-34.5</v>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="N9" s="8">
+        <v>160</v>
       </c>
       <c r="O9" s="8">
-        <v>621</v>
+        <v>3339.6</v>
       </c>
       <c r="P9" s="9">
-        <v>1.2E-2</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="Q9" s="8">
-        <v>621</v>
+        <v>1579.8</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C10" s="7">
-        <v>145</v>
+        <v>115.5</v>
       </c>
       <c r="D10" s="7">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E10" s="7">
-        <v>117.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>20</v>
-      </c>
-      <c r="G10" s="8">
-        <v>16</v>
+        <v>115</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-29.5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>-20.34</v>
       </c>
       <c r="H10" s="9">
-        <v>1.84E-2</v>
-      </c>
-      <c r="I10" s="8">
-        <v>19.8</v>
+        <v>1.2E-2</v>
+      </c>
+      <c r="I10" s="10">
+        <v>-34.5</v>
       </c>
       <c r="J10" s="8">
-        <v>771.1</v>
+        <v>621</v>
       </c>
       <c r="K10" s="9">
-        <v>0.38200000000000001</v>
+        <v>1.2E-2</v>
       </c>
       <c r="L10" s="8">
-        <v>996.8</v>
+        <v>621</v>
       </c>
       <c r="M10" s="9">
-        <v>1.84E-2</v>
-      </c>
-      <c r="N10" s="8">
-        <v>19.8</v>
+        <v>1.2E-2</v>
+      </c>
+      <c r="N10" s="10">
+        <v>-34.5</v>
       </c>
       <c r="O10" s="8">
-        <v>771.1</v>
+        <v>621</v>
       </c>
       <c r="P10" s="9">
-        <v>0.38200000000000001</v>
+        <v>1.2E-2</v>
       </c>
       <c r="Q10" s="8">
-        <v>996.8</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>132.5</v>
+        <v>125</v>
       </c>
       <c r="C11" s="7">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="D11" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E11" s="7">
-        <v>114</v>
-      </c>
-      <c r="F11" s="10">
-        <v>-7.5</v>
-      </c>
-      <c r="G11" s="10">
-        <v>-5.66</v>
+        <v>117.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>20</v>
+      </c>
+      <c r="G11" s="8">
+        <v>16</v>
       </c>
       <c r="H11" s="9">
-        <v>1.5299999999999999E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="I11" s="8">
-        <v>132.80000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="J11" s="8">
-        <v>922.7</v>
+        <v>771.1</v>
       </c>
       <c r="K11" s="9">
-        <v>0.36399999999999999</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="L11" s="8">
-        <v>1011.3</v>
+        <v>996.8</v>
       </c>
       <c r="M11" s="9">
-        <v>1.5299999999999999E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="N11" s="8">
-        <v>132.80000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="O11" s="8">
-        <v>922.7</v>
+        <v>771.1</v>
       </c>
       <c r="P11" s="9">
-        <v>0.36399999999999999</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="Q11" s="8">
-        <v>1011.3</v>
+        <v>996.8</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>171</v>
+        <v>132.5</v>
       </c>
       <c r="C12" s="7">
-        <v>132.5</v>
+        <v>125</v>
       </c>
       <c r="D12" s="7">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="E12" s="7">
-        <v>122.5</v>
+        <v>114</v>
       </c>
       <c r="F12" s="10">
-        <v>-38.5</v>
+        <v>-7.5</v>
       </c>
       <c r="G12" s="10">
-        <v>-22.51</v>
+        <v>-5.66</v>
       </c>
       <c r="H12" s="9">
-        <v>6.6E-3</v>
-      </c>
-      <c r="I12" s="10">
-        <v>-81</v>
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="I12" s="8">
+        <v>132.80000000000001</v>
       </c>
       <c r="J12" s="8">
-        <v>1244.9000000000001</v>
+        <v>922.7</v>
       </c>
       <c r="K12" s="9">
-        <v>0.34899999999999998</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="L12" s="8">
-        <v>1015.9</v>
+        <v>1011.3</v>
       </c>
       <c r="M12" s="9">
-        <v>6.6E-3</v>
-      </c>
-      <c r="N12" s="10">
-        <v>-81</v>
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="N12" s="8">
+        <v>132.80000000000001</v>
       </c>
       <c r="O12" s="8">
-        <v>1244.9000000000001</v>
+        <v>922.7</v>
       </c>
       <c r="P12" s="9">
-        <v>0.34899999999999998</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="Q12" s="8">
-        <v>1015.9</v>
+        <v>1011.3</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="C13" s="7">
-        <v>171</v>
+        <v>132.5</v>
       </c>
       <c r="D13" s="7">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="E13" s="7">
-        <v>43.8</v>
+        <v>122.5</v>
       </c>
       <c r="F13" s="10">
-        <v>-30</v>
+        <v>-38.5</v>
       </c>
       <c r="G13" s="10">
-        <v>-14.93</v>
+        <v>-22.51</v>
       </c>
       <c r="H13" s="9">
-        <v>3.4700000000000002E-2</v>
-      </c>
-      <c r="I13" s="8">
-        <v>185.5</v>
+        <v>6.6E-3</v>
+      </c>
+      <c r="I13" s="10">
+        <v>-81</v>
       </c>
       <c r="J13" s="8">
-        <v>6212.7</v>
+        <v>1244.9000000000001</v>
       </c>
       <c r="K13" s="9">
-        <v>0.34200000000000003</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="L13" s="8">
-        <v>1012.2</v>
+        <v>1015.9</v>
       </c>
       <c r="M13" s="9">
-        <v>3.4700000000000002E-2</v>
-      </c>
-      <c r="N13" s="8">
-        <v>185.5</v>
+        <v>6.6E-3</v>
+      </c>
+      <c r="N13" s="10">
+        <v>-81</v>
       </c>
       <c r="O13" s="8">
-        <v>6212.7</v>
+        <v>1244.9000000000001</v>
       </c>
       <c r="P13" s="9">
-        <v>0.34200000000000003</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="Q13" s="8">
-        <v>1012.2</v>
+        <v>1015.9</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>17</v>
+        <v>44440</v>
+      </c>
+      <c r="B14" s="7">
+        <v>201</v>
+      </c>
+      <c r="C14" s="7">
+        <v>171</v>
+      </c>
+      <c r="D14" s="7">
+        <v>230</v>
+      </c>
+      <c r="E14" s="7">
+        <v>43.8</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-30</v>
+      </c>
+      <c r="G14" s="10">
+        <v>-14.93</v>
       </c>
       <c r="H14" s="9">
-        <v>1.2200000000000001E-2</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="I14" s="8">
-        <v>170.2</v>
+        <v>185.5</v>
       </c>
       <c r="J14" s="8">
-        <v>2381.6</v>
+        <v>6212.7</v>
       </c>
       <c r="K14" s="9">
-        <v>0.307</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="L14" s="8">
-        <v>917.5</v>
+        <v>1012.2</v>
       </c>
       <c r="M14" s="9">
-        <v>1.2200000000000001E-2</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="N14" s="8">
-        <v>170.2</v>
+        <v>185.5</v>
       </c>
       <c r="O14" s="8">
-        <v>2381.6</v>
+        <v>6212.7</v>
       </c>
       <c r="P14" s="9">
-        <v>0.307</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="Q14" s="8">
-        <v>917.5</v>
+        <v>1012.2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1934,39 +1934,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>4.4999999999999997E-3</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="I15" s="8">
-        <v>21</v>
+        <v>170.2</v>
       </c>
       <c r="J15" s="8">
-        <v>749</v>
+        <v>2381.6</v>
       </c>
       <c r="K15" s="9">
-        <v>0.29499999999999998</v>
+        <v>0.307</v>
       </c>
       <c r="L15" s="8">
-        <v>893.4</v>
+        <v>917.5</v>
       </c>
       <c r="M15" s="9">
-        <v>4.4999999999999997E-3</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="N15" s="8">
-        <v>21</v>
+        <v>170.2</v>
       </c>
       <c r="O15" s="8">
-        <v>749</v>
+        <v>2381.6</v>
       </c>
       <c r="P15" s="9">
-        <v>0.29499999999999998</v>
+        <v>0.307</v>
       </c>
       <c r="Q15" s="8">
-        <v>893.4</v>
+        <v>917.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1987,33 +1987,86 @@
         <v>17</v>
       </c>
       <c r="H16" s="9">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="I16" s="8">
+        <v>21</v>
+      </c>
+      <c r="J16" s="8">
+        <v>749</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="L16" s="8">
+        <v>893.4</v>
+      </c>
+      <c r="M16" s="9">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="N16" s="8">
+        <v>21</v>
+      </c>
+      <c r="O16" s="8">
+        <v>749</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>893.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>44348</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="9">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J17" s="10">
         <v>-84.7</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K17" s="9">
         <v>0.29099999999999998</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L17" s="8">
         <v>896</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M17" s="9">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="N17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O17" s="10">
         <v>-84.7</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P17" s="9">
         <v>0.29099999999999998</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q17" s="8">
         <v>896</v>
       </c>
     </row>
